--- a/public/exports-from-60-with-coowners/29189803.xlsx
+++ b/public/exports-from-60-with-coowners/29189803.xlsx
@@ -26089,12 +26089,12 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041324</t>
+          <t xml:space="preserve">311041311</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -26479,12 +26479,12 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319330</t>
+          <t xml:space="preserve">311319327</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442081</t>
+          <t xml:space="preserve">311442101</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624659</t>
+          <t xml:space="preserve">311624658</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -42139,7 +42139,7 @@
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
@@ -42214,7 +42214,7 @@
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759943</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
